--- a/Exp3_PTO_GRPO/eda/results/tables/stats/stats.xlsx
+++ b/Exp3_PTO_GRPO/eda/results/tables/stats/stats.xlsx
@@ -514,36 +514,36 @@
         <v>3.067</v>
       </c>
       <c r="D2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E2" t="n">
-        <v>4.082</v>
+        <v>3.753</v>
       </c>
       <c r="F2" t="n">
-        <v>1.016</v>
+        <v>0.6860000000000001</v>
       </c>
       <c r="G2" t="n">
-        <v>1.22</v>
+        <v>0.721</v>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I2" t="n">
         <v>0</v>
       </c>
       <c r="J2" t="n">
-        <v>0.851</v>
+        <v>0.501</v>
       </c>
       <c r="K2" t="n">
-        <v>1.185</v>
+        <v>0.882</v>
       </c>
       <c r="L2" t="n">
-        <v>0.287</v>
+        <v>0.196</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1278</v>
+        <v>0.0716</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -564,16 +564,16 @@
         <v>2.89</v>
       </c>
       <c r="D3" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E3" t="n">
-        <v>3.374</v>
+        <v>3.438</v>
       </c>
       <c r="F3" t="n">
-        <v>0.484</v>
+        <v>0.549</v>
       </c>
       <c r="G3" t="n">
-        <v>0.828</v>
+        <v>0.837</v>
       </c>
       <c r="H3" t="inlineStr">
         <is>
@@ -584,16 +584,16 @@
         <v>0</v>
       </c>
       <c r="J3" t="n">
-        <v>0.372</v>
+        <v>0.424</v>
       </c>
       <c r="K3" t="n">
-        <v>0.609</v>
+        <v>0.68</v>
       </c>
       <c r="L3" t="n">
-        <v>0.162</v>
+        <v>0.141</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0576</v>
+        <v>0.0395</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -614,16 +614,16 @@
         <v>2.362</v>
       </c>
       <c r="D4" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E4" t="n">
-        <v>2.749</v>
+        <v>2.773</v>
       </c>
       <c r="F4" t="n">
-        <v>0.387</v>
+        <v>0.411</v>
       </c>
       <c r="G4" t="n">
-        <v>0.636</v>
+        <v>0.593</v>
       </c>
       <c r="H4" t="inlineStr">
         <is>
@@ -634,16 +634,16 @@
         <v>0</v>
       </c>
       <c r="J4" t="n">
-        <v>0.27</v>
+        <v>0.272</v>
       </c>
       <c r="K4" t="n">
-        <v>0.51</v>
+        <v>0.555</v>
       </c>
       <c r="L4" t="n">
-        <v>0.113</v>
+        <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0447</v>
+        <v>0.0241</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -664,16 +664,16 @@
         <v>2.71</v>
       </c>
       <c r="D5" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E5" t="n">
-        <v>3.326</v>
+        <v>3.319</v>
       </c>
       <c r="F5" t="n">
-        <v>0.616</v>
+        <v>0.609</v>
       </c>
       <c r="G5" t="n">
-        <v>0.767</v>
+        <v>0.592</v>
       </c>
       <c r="H5" t="inlineStr">
         <is>
@@ -684,16 +684,16 @@
         <v>0</v>
       </c>
       <c r="J5" t="n">
-        <v>0.463</v>
+        <v>0.413</v>
       </c>
       <c r="K5" t="n">
-        <v>0.778</v>
+        <v>0.8159999999999999</v>
       </c>
       <c r="L5" t="n">
-        <v>0.146</v>
+        <v>0.104</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0725</v>
+        <v>0.0396</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -714,16 +714,16 @@
         <v>3.224</v>
       </c>
       <c r="D6" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E6" t="n">
-        <v>4.234</v>
+        <v>3.922</v>
       </c>
       <c r="F6" t="n">
-        <v>1.01</v>
+        <v>0.698</v>
       </c>
       <c r="G6" t="n">
-        <v>1.364</v>
+        <v>0.823</v>
       </c>
       <c r="H6" t="inlineStr">
         <is>
@@ -734,16 +734,16 @@
         <v>0</v>
       </c>
       <c r="J6" t="n">
-        <v>0.875</v>
+        <v>0.531</v>
       </c>
       <c r="K6" t="n">
-        <v>1.162</v>
+        <v>0.87</v>
       </c>
       <c r="L6" t="n">
-        <v>0.352</v>
+        <v>0.258</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1255</v>
+        <v>0.0784</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -764,16 +764,16 @@
         <v>0.487</v>
       </c>
       <c r="D7" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E7" t="n">
-        <v>0.572</v>
+        <v>0.574</v>
       </c>
       <c r="F7" t="n">
-        <v>0.08500000000000001</v>
+        <v>0.08699999999999999</v>
       </c>
       <c r="G7" t="n">
-        <v>0.34</v>
+        <v>0.363</v>
       </c>
       <c r="H7" t="inlineStr">
         <is>
@@ -781,22 +781,22 @@
         </is>
       </c>
       <c r="I7" t="n">
-        <v>0.0034</v>
+        <v>0.001</v>
       </c>
       <c r="J7" t="n">
-        <v>0.035</v>
+        <v>0.04</v>
       </c>
       <c r="K7" t="n">
-        <v>0.134</v>
+        <v>0.135</v>
       </c>
       <c r="L7" t="n">
-        <v>0.079</v>
+        <v>0.048</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0097</v>
+        <v>0.0046</v>
       </c>
       <c r="N7" t="n">
-        <v>0.0034</v>
+        <v>0.001</v>
       </c>
     </row>
     <row r="8">
@@ -814,16 +814,16 @@
         <v>0.211</v>
       </c>
       <c r="D8" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E8" t="n">
-        <v>0.535</v>
+        <v>0.838</v>
       </c>
       <c r="F8" t="n">
-        <v>0.324</v>
+        <v>0.626</v>
       </c>
       <c r="G8" t="n">
-        <v>0.889</v>
+        <v>1.717</v>
       </c>
       <c r="H8" t="inlineStr">
         <is>
@@ -834,16 +834,16 @@
         <v>0</v>
       </c>
       <c r="J8" t="n">
-        <v>0.251</v>
+        <v>0.551</v>
       </c>
       <c r="K8" t="n">
-        <v>0.394</v>
+        <v>0.699</v>
       </c>
       <c r="L8" t="n">
-        <v>0.336</v>
+        <v>0.479</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0273</v>
+        <v>0.0437</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -864,36 +864,36 @@
         <v>3.021</v>
       </c>
       <c r="D9" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E9" t="n">
-        <v>3.935</v>
+        <v>3.606</v>
       </c>
       <c r="F9" t="n">
-        <v>0.915</v>
+        <v>0.585</v>
       </c>
       <c r="G9" t="n">
-        <v>1.129</v>
+        <v>0.577</v>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>large</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="I9" t="n">
         <v>0</v>
       </c>
       <c r="J9" t="n">
-        <v>0.754</v>
+        <v>0.392</v>
       </c>
       <c r="K9" t="n">
-        <v>1.081</v>
+        <v>0.8</v>
       </c>
       <c r="L9" t="n">
-        <v>0.225</v>
+        <v>0.132</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1152</v>
+        <v>0.0561</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -914,16 +914,16 @@
         <v>3.113</v>
       </c>
       <c r="D10" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="E10" t="n">
-        <v>4.229</v>
+        <v>3.899</v>
       </c>
       <c r="F10" t="n">
-        <v>1.116</v>
+        <v>0.786</v>
       </c>
       <c r="G10" t="n">
-        <v>1.209</v>
+        <v>0.824</v>
       </c>
       <c r="H10" t="inlineStr">
         <is>
@@ -934,16 +934,16 @@
         <v>0</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9399999999999999</v>
+        <v>0.605</v>
       </c>
       <c r="K10" t="n">
-        <v>1.305</v>
+        <v>0.973</v>
       </c>
       <c r="L10" t="n">
-        <v>0.349</v>
+        <v>0.26</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1403</v>
+        <v>0.0871</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -2119,16 +2119,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>0.2866</v>
+        <v>0.196</v>
       </c>
       <c r="D2" t="n">
-        <v>0.1278</v>
+        <v>0.0716</v>
       </c>
       <c r="E2" t="n">
         <v>8</v>
       </c>
       <c r="F2" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3">
@@ -2212,7 +2212,7 @@
         </is>
       </c>
       <c r="B2" t="n">
-        <v>55.7</v>
+        <v>55</v>
       </c>
     </row>
     <row r="3">
@@ -2372,10 +2372,10 @@
         <v>1.185</v>
       </c>
       <c r="L2" t="n">
-        <v>0.287</v>
+        <v>0.196</v>
       </c>
       <c r="M2" t="n">
-        <v>0.1278</v>
+        <v>0.0716</v>
       </c>
       <c r="N2" t="n">
         <v>0</v>
@@ -2422,10 +2422,10 @@
         <v>0.609</v>
       </c>
       <c r="L3" t="n">
-        <v>0.162</v>
+        <v>0.141</v>
       </c>
       <c r="M3" t="n">
-        <v>0.0576</v>
+        <v>0.0395</v>
       </c>
       <c r="N3" t="n">
         <v>0</v>
@@ -2472,10 +2472,10 @@
         <v>0.51</v>
       </c>
       <c r="L4" t="n">
-        <v>0.113</v>
+        <v>0.08</v>
       </c>
       <c r="M4" t="n">
-        <v>0.0447</v>
+        <v>0.0241</v>
       </c>
       <c r="N4" t="n">
         <v>0</v>
@@ -2522,10 +2522,10 @@
         <v>0.778</v>
       </c>
       <c r="L5" t="n">
-        <v>0.146</v>
+        <v>0.104</v>
       </c>
       <c r="M5" t="n">
-        <v>0.0725</v>
+        <v>0.0396</v>
       </c>
       <c r="N5" t="n">
         <v>0</v>
@@ -2572,10 +2572,10 @@
         <v>1.162</v>
       </c>
       <c r="L6" t="n">
-        <v>0.352</v>
+        <v>0.258</v>
       </c>
       <c r="M6" t="n">
-        <v>0.1255</v>
+        <v>0.0784</v>
       </c>
       <c r="N6" t="n">
         <v>0</v>
@@ -2622,10 +2622,10 @@
         <v>0.134</v>
       </c>
       <c r="L7" t="n">
-        <v>0.079</v>
+        <v>0.048</v>
       </c>
       <c r="M7" t="n">
-        <v>0.0097</v>
+        <v>0.0046</v>
       </c>
       <c r="N7" t="n">
         <v>0.0034</v>
@@ -2672,10 +2672,10 @@
         <v>0.394</v>
       </c>
       <c r="L8" t="n">
-        <v>0.336</v>
+        <v>0.479</v>
       </c>
       <c r="M8" t="n">
-        <v>0.0273</v>
+        <v>0.0437</v>
       </c>
       <c r="N8" t="n">
         <v>0</v>
@@ -2722,10 +2722,10 @@
         <v>1.081</v>
       </c>
       <c r="L9" t="n">
-        <v>0.225</v>
+        <v>0.132</v>
       </c>
       <c r="M9" t="n">
-        <v>0.1152</v>
+        <v>0.0561</v>
       </c>
       <c r="N9" t="n">
         <v>0</v>
@@ -2772,10 +2772,10 @@
         <v>1.305</v>
       </c>
       <c r="L10" t="n">
-        <v>0.349</v>
+        <v>0.26</v>
       </c>
       <c r="M10" t="n">
-        <v>0.1403</v>
+        <v>0.0871</v>
       </c>
       <c r="N10" t="n">
         <v>0</v>
@@ -3744,16 +3744,16 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>303.7085</v>
+        <v>312.7165</v>
       </c>
       <c r="D2" t="n">
         <v>0</v>
       </c>
       <c r="E2" t="n">
-        <v>0.3955</v>
+        <v>0.3257</v>
       </c>
       <c r="F2" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G2" t="n">
         <v>96</v>
@@ -3771,16 +3771,16 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>119.5167</v>
+        <v>166.3047</v>
       </c>
       <c r="D3" t="n">
         <v>0</v>
       </c>
       <c r="E3" t="n">
-        <v>0.1556</v>
+        <v>0.1732</v>
       </c>
       <c r="F3" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G3" t="n">
         <v>96</v>
@@ -3798,16 +3798,16 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>91.3616</v>
+        <v>111.1489</v>
       </c>
       <c r="D4" t="n">
         <v>0</v>
       </c>
       <c r="E4" t="n">
-        <v>0.119</v>
+        <v>0.1158</v>
       </c>
       <c r="F4" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G4" t="n">
         <v>96</v>
@@ -3825,16 +3825,16 @@
         </is>
       </c>
       <c r="C5" t="n">
-        <v>103.7254</v>
+        <v>129.4716</v>
       </c>
       <c r="D5" t="n">
         <v>0</v>
       </c>
       <c r="E5" t="n">
-        <v>0.1351</v>
+        <v>0.1349</v>
       </c>
       <c r="F5" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G5" t="n">
         <v>96</v>
@@ -3852,16 +3852,16 @@
         </is>
       </c>
       <c r="C6" t="n">
-        <v>294.8508</v>
+        <v>303.5148</v>
       </c>
       <c r="D6" t="n">
         <v>0</v>
       </c>
       <c r="E6" t="n">
-        <v>0.3839</v>
+        <v>0.3162</v>
       </c>
       <c r="F6" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G6" t="n">
         <v>96</v>
@@ -3879,16 +3879,16 @@
         </is>
       </c>
       <c r="C7" t="n">
-        <v>33.4649</v>
+        <v>58.1104</v>
       </c>
       <c r="D7" t="n">
-        <v>0.0001</v>
+        <v>0</v>
       </c>
       <c r="E7" t="n">
-        <v>0.0436</v>
+        <v>0.0605</v>
       </c>
       <c r="F7" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G7" t="n">
         <v>96</v>
@@ -3906,16 +3906,16 @@
         </is>
       </c>
       <c r="C8" t="n">
-        <v>140.8609</v>
+        <v>335.2027</v>
       </c>
       <c r="D8" t="n">
         <v>0</v>
       </c>
       <c r="E8" t="n">
-        <v>0.1834</v>
+        <v>0.3492</v>
       </c>
       <c r="F8" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G8" t="n">
         <v>96</v>
@@ -3933,16 +3933,16 @@
         </is>
       </c>
       <c r="C9" t="n">
-        <v>250.5564</v>
+        <v>265.6537</v>
       </c>
       <c r="D9" t="n">
         <v>0</v>
       </c>
       <c r="E9" t="n">
-        <v>0.3262</v>
+        <v>0.2767</v>
       </c>
       <c r="F9" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G9" t="n">
         <v>96</v>
@@ -3960,16 +3960,16 @@
         </is>
       </c>
       <c r="C10" t="n">
-        <v>312.3654</v>
+        <v>329.8852</v>
       </c>
       <c r="D10" t="n">
         <v>0</v>
       </c>
       <c r="E10" t="n">
-        <v>0.4067</v>
+        <v>0.3436</v>
       </c>
       <c r="F10" t="n">
-        <v>9</v>
+        <v>11</v>
       </c>
       <c r="G10" t="n">
         <v>96</v>
@@ -4472,7 +4472,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H9"/>
+  <dimension ref="A1:H11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -4723,6 +4723,58 @@
       </c>
       <c r="H9" t="n">
         <v>1.1852</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>9</v>
+      </c>
+      <c r="B10" t="n">
+        <v>96</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.7407</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.7912</v>
+      </c>
+      <c r="E10" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" t="n">
+        <v>0</v>
+      </c>
+      <c r="G10" t="n">
+        <v>0.5553</v>
+      </c>
+      <c r="H10" t="n">
+        <v>0.9229000000000001</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>10</v>
+      </c>
+      <c r="B11" t="n">
+        <v>96</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.6858</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.7207</v>
+      </c>
+      <c r="E11" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" t="n">
+        <v>0</v>
+      </c>
+      <c r="G11" t="n">
+        <v>0.5014999999999999</v>
+      </c>
+      <c r="H11" t="n">
+        <v>0.8817</v>
       </c>
     </row>
   </sheetData>
@@ -5212,7 +5264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F73"/>
+  <dimension ref="A1:F91"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6829,6 +6881,402 @@
       </c>
       <c r="F73" t="n">
         <v>0.2999</v>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="n">
+        <v>9</v>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="C74" t="n">
+        <v>96</v>
+      </c>
+      <c r="D74" t="n">
+        <v>0.4309</v>
+      </c>
+      <c r="E74" t="n">
+        <v>0.7732</v>
+      </c>
+      <c r="F74" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="n">
+        <v>9</v>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>WAI-SR</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>96</v>
+      </c>
+      <c r="D75" t="n">
+        <v>0.4479</v>
+      </c>
+      <c r="E75" t="n">
+        <v>0.717</v>
+      </c>
+      <c r="F75" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="n">
+        <v>9</v>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>CSQ-8</t>
+        </is>
+      </c>
+      <c r="C76" t="n">
+        <v>96</v>
+      </c>
+      <c r="D76" t="n">
+        <v>0.4948</v>
+      </c>
+      <c r="E76" t="n">
+        <v>0.8073</v>
+      </c>
+      <c r="F76" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="n">
+        <v>9</v>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>MI-SAT</t>
+        </is>
+      </c>
+      <c r="C77" t="n">
+        <v>96</v>
+      </c>
+      <c r="D77" t="n">
+        <v>0.6632</v>
+      </c>
+      <c r="E77" t="n">
+        <v>0.8349</v>
+      </c>
+      <c r="F77" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="n">
+        <v>9</v>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="C78" t="n">
+        <v>96</v>
+      </c>
+      <c r="D78" t="n">
+        <v>0.3047</v>
+      </c>
+      <c r="E78" t="n">
+        <v>0.6438</v>
+      </c>
+      <c r="F78" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="n">
+        <v>9</v>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="C79" t="n">
+        <v>96</v>
+      </c>
+      <c r="D79" t="n">
+        <v>0.1618</v>
+      </c>
+      <c r="E79" t="n">
+        <v>0.7262999999999999</v>
+      </c>
+      <c r="F79" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="n">
+        <v>9</v>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="C80" t="n">
+        <v>96</v>
+      </c>
+      <c r="D80" t="n">
+        <v>0.1209</v>
+      </c>
+      <c r="E80" t="n">
+        <v>0.4043</v>
+      </c>
+      <c r="F80" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="n">
+        <v>9</v>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C81" t="n">
+        <v>96</v>
+      </c>
+      <c r="D81" t="n">
+        <v>0.5917</v>
+      </c>
+      <c r="E81" t="n">
+        <v>0.9056</v>
+      </c>
+      <c r="F81" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="n">
+        <v>9</v>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C82" t="n">
+        <v>96</v>
+      </c>
+      <c r="D82" t="n">
+        <v>0.2702</v>
+      </c>
+      <c r="E82" t="n">
+        <v>0.5116000000000001</v>
+      </c>
+      <c r="F82" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="n">
+        <v>10</v>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>Q1Q2</t>
+        </is>
+      </c>
+      <c r="C83" t="n">
+        <v>96</v>
+      </c>
+      <c r="D83" t="n">
+        <v>0.5072</v>
+      </c>
+      <c r="E83" t="n">
+        <v>0.7287</v>
+      </c>
+      <c r="F83" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="n">
+        <v>10</v>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>WAI-SR</t>
+        </is>
+      </c>
+      <c r="C84" t="n">
+        <v>96</v>
+      </c>
+      <c r="D84" t="n">
+        <v>0.059</v>
+      </c>
+      <c r="E84" t="n">
+        <v>0.1174</v>
+      </c>
+      <c r="F84" t="n">
+        <v>0.2418</v>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="n">
+        <v>10</v>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>CSQ-8</t>
+        </is>
+      </c>
+      <c r="C85" t="n">
+        <v>96</v>
+      </c>
+      <c r="D85" t="n">
+        <v>0.1719</v>
+      </c>
+      <c r="E85" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="F85" t="n">
+        <v>0.0146</v>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>10</v>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>MI-SAT</t>
+        </is>
+      </c>
+      <c r="C86" t="n">
+        <v>96</v>
+      </c>
+      <c r="D86" t="n">
+        <v>0.217</v>
+      </c>
+      <c r="E86" t="n">
+        <v>0.2817</v>
+      </c>
+      <c r="F86" t="n">
+        <v>0.0146</v>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>10</v>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>MITI</t>
+        </is>
+      </c>
+      <c r="C87" t="n">
+        <v>96</v>
+      </c>
+      <c r="D87" t="n">
+        <v>0.3516</v>
+      </c>
+      <c r="E87" t="n">
+        <v>0.4586</v>
+      </c>
+      <c r="F87" t="n">
+        <v>0.0001</v>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>10</v>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>PCT</t>
+        </is>
+      </c>
+      <c r="C88" t="n">
+        <v>96</v>
+      </c>
+      <c r="D88" t="n">
+        <v>0.056</v>
+      </c>
+      <c r="E88" t="n">
+        <v>0.2875</v>
+      </c>
+      <c r="F88" t="n">
+        <v>0.0146</v>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="n">
+        <v>10</v>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>MICI</t>
+        </is>
+      </c>
+      <c r="C89" t="n">
+        <v>96</v>
+      </c>
+      <c r="D89" t="n">
+        <v>-0.3463</v>
+      </c>
+      <c r="E89" t="n">
+        <v>-0.9893</v>
+      </c>
+      <c r="F89" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>10</v>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>Q1</t>
+        </is>
+      </c>
+      <c r="C90" t="n">
+        <v>96</v>
+      </c>
+      <c r="D90" t="n">
+        <v>0.5333</v>
+      </c>
+      <c r="E90" t="n">
+        <v>0.7076</v>
+      </c>
+      <c r="F90" t="n">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>10</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>Q2</t>
+        </is>
+      </c>
+      <c r="C91" t="n">
+        <v>96</v>
+      </c>
+      <c r="D91" t="n">
+        <v>0.481</v>
+      </c>
+      <c r="E91" t="n">
+        <v>0.6997</v>
+      </c>
+      <c r="F91" t="n">
+        <v>0</v>
       </c>
     </row>
   </sheetData>
